--- a/e_commerce_forms/003_paypal_purchase_order_form--e_commerce_forms.xlsx
+++ b/e_commerce_forms/003_paypal_purchase_order_form--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>paypal_currency</t>
+          <t>paypal_currency_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Paypal Currency 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Paypal Submit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Paypal Failure</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1181,7 +1181,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>paypal_currency_choices</t>
+          <t>paypal_currency_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>paypal_currency_choices</t>
+          <t>paypal_currency_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>paypal_currency_choices</t>
+          <t>paypal_currency_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
